--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104746_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104746_W32.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6997</v>
+        <v>5.2048</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6769</v>
+        <v>10.0065</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.9773</v>
+        <v>-4.8016</v>
       </c>
       <c r="G2" t="n">
-        <v>8.0528</v>
+        <v>8.044600000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0699</v>
+        <v>1.071</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9829</v>
+        <v>6.9736</v>
       </c>
       <c r="J2" t="n">
-        <v>11.4186</v>
+        <v>11.3981</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5576</v>
+        <v>2.5511</v>
       </c>
       <c r="L2" t="n">
-        <v>8.860900000000001</v>
+        <v>8.847</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.3658</v>
+        <v>-3.3535</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4877</v>
+        <v>-1.48</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.878</v>
+        <v>-1.8734</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4891</v>
+        <v>0.0221</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6057</v>
+        <v>-0.2535</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1166</v>
+        <v>0.2755</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4343</v>
+        <v>3.1065</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3991</v>
+        <v>6.0798</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9649</v>
+        <v>-2.9734</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.385</v>
+        <v>-0.3811</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2225</v>
+        <v>-1.2182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8375</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6449</v>
+        <v>3.6343</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3021</v>
+        <v>1.296</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3427</v>
+        <v>2.3383</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.0298</v>
+        <v>-4.0153</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5246</v>
+        <v>-2.5142</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5052</v>
+        <v>-1.5011</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6833</v>
+        <v>0.3494</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5718</v>
+        <v>0.2666</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1115</v>
+        <v>0.0827</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1643</v>
+        <v>-0.2247</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6044</v>
+        <v>1.6869</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7686</v>
+        <v>-1.9116</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9679</v>
+        <v>-0.9831</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5719</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5398</v>
+        <v>-1.537</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2805</v>
+        <v>2.2561</v>
       </c>
       <c r="K4" t="n">
-        <v>1.684</v>
+        <v>1.6603</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5965</v>
+        <v>0.5958</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2484</v>
+        <v>-3.2392</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.112</v>
+        <v>-1.1064</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1363</v>
+        <v>-2.1328</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4701</v>
+        <v>-0.51</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5867</v>
+        <v>-0.4718</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1166</v>
+        <v>-0.0381</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7126</v>
+        <v>-0.594</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6893</v>
+        <v>0.7981</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4019</v>
+        <v>-1.3921</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8199</v>
+        <v>-0.8192</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8858</v>
+        <v>-0.8847</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0659</v>
+        <v>0.0655</v>
       </c>
       <c r="J5" t="n">
-        <v>1.295</v>
+        <v>1.2885</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3689</v>
+        <v>0.3652</v>
       </c>
       <c r="L5" t="n">
-        <v>0.926</v>
+        <v>0.9233</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1149</v>
+        <v>-2.1077</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2548</v>
+        <v>-1.2499</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8601</v>
+        <v>-0.8578</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5742</v>
+        <v>-0.4577</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6057</v>
+        <v>-0.4904</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0315</v>
+        <v>0.0327</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0671</v>
+        <v>-0.9367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0818</v>
+        <v>-0.0829</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9853</v>
+        <v>-0.8538</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2391</v>
+        <v>0.2408</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.151</v>
+        <v>-0.1495</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3901</v>
+        <v>0.3903</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1264</v>
+        <v>0.1262</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1127</v>
+        <v>0.1146</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2029</v>
+        <v>-0.2012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3156</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2827</v>
+        <v>-0.1579</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2082</v>
+        <v>-0.2091</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0745</v>
+        <v>0.0512</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4496</v>
+        <v>-1.3272</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0514</v>
+        <v>0.0569</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3982</v>
+        <v>-1.3841</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1106</v>
+        <v>-2.1102</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7348</v>
+        <v>0.7351</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8454</v>
+        <v>-2.8453</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6631</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4862</v>
+        <v>1.4824</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.143</v>
+        <v>-2.1455</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4537</v>
+        <v>-1.4471</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7514</v>
+        <v>-0.7472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7023</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3156</v>
+        <v>-0.1974</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4858</v>
+        <v>-0.3695</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1703</v>
+        <v>0.1721</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6422</v>
+        <v>-1.4703</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9129</v>
+        <v>-1.6555</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5552</v>
+        <v>0.1852</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0476</v>
+        <v>0.0132</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5883</v>
+        <v>-1.1605</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4593</v>
+        <v>1.1736</v>
       </c>
       <c r="J8" t="n">
-        <v>1.506</v>
+        <v>2.1337</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2451</v>
+        <v>-0.0107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.261</v>
+        <v>2.1444</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5536</v>
+        <v>-2.1205</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8334</v>
+        <v>-1.1497</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7203</v>
+        <v>-0.9708</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2272</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9087</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3137</v>
+        <v>-0.4332</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1328</v>
+        <v>-0.6902</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1809</v>
+        <v>0.257</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4101</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7302</v>
+        <v>-1.6965</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1002</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6311</v>
+        <v>-1.5964</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.385</v>
+        <v>-1.3818</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4989</v>
+        <v>-0.4971</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8861</v>
+        <v>-0.8847</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1091</v>
+        <v>0.1089</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4941</v>
+        <v>-1.4907</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5335</v>
+        <v>-0.5315</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9607</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3452</v>
+        <v>-0.3148</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2082</v>
+        <v>-0.2091</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8495</v>
+        <v>-1.9129</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.985</v>
+        <v>1.6538</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1355</v>
+        <v>-3.5668</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0133</v>
+        <v>-2.0461</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1623</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1757</v>
+        <v>-1.4549</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1451</v>
+        <v>1.4942</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0052</v>
+        <v>1.2336</v>
       </c>
       <c r="L10" t="n">
-        <v>2.1503</v>
+        <v>0.2607</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1318</v>
+        <v>-3.5403</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1571</v>
+        <v>-1.8248</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9746</v>
+        <v>-1.7155</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3631</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0447</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8185</v>
+        <v>0.0452</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0411</v>
+        <v>-0.1072</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2226</v>
+        <v>0.1524</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3188</v>
+        <v>1.405</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4599</v>
+        <v>-3.159</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2577</v>
+        <v>-0.8787</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2022</v>
+        <v>-2.2803</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3329</v>
+        <v>-3.9184</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4268</v>
+        <v>-1.0319</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9061</v>
+        <v>-2.8865</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5636</v>
+        <v>-0.3649</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6755</v>
+        <v>0.2758</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1118</v>
+        <v>-0.6407</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7693</v>
+        <v>-3.5535</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7514</v>
+        <v>-1.3077</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0179</v>
+        <v>-2.2458</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3631</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3631</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3988</v>
+        <v>-0.3787</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5138</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2952</v>
+        <v>0.135</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5251</v>
+        <v>-3.4609</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2276</v>
+        <v>-2.1463</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2975</v>
+        <v>-1.3145</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.929</v>
+        <v>-3.3307</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0384</v>
+        <v>-2.4267</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8906</v>
+        <v>-0.904</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3633</v>
+        <v>-1.5677</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2765</v>
+        <v>-1.6795</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6398</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5658</v>
+        <v>-1.7629</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3149</v>
+        <v>-0.7472</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2508</v>
+        <v>-1.0157</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.732</v>
+        <v>-0.4065</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.5786</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1324</v>
+        <v>0.1721</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.466499999999999</v>
+        <v>-6.4709</v>
       </c>
       <c r="E13" t="n">
-        <v>15.58</v>
+        <v>15.4184</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.0467</v>
+        <v>-21.8894</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.6727</v>
+        <v>-6.671999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.5974</v>
+        <v>-5.5998</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0752</v>
+        <v>-1.0722</v>
       </c>
       <c r="J13" t="n">
-        <v>19.9419</v>
+        <v>19.8443</v>
       </c>
       <c r="K13" t="n">
-        <v>7.3261</v>
+        <v>7.260400000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>12.6156</v>
+        <v>12.584</v>
       </c>
       <c r="M13" t="n">
-        <v>-26.6145</v>
+        <v>-26.51609999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.9237</v>
+        <v>-12.8598</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.6906</v>
+        <v>-13.656</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4078</v>
+        <v>3.4146</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.951499999999999</v>
+        <v>-7.967200000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3593</v>
+        <v>11.3817</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4292</v>
+        <v>-2.4395</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5953</v>
+        <v>-3.6266</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1661</v>
+        <v>1.1869</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7725</v>
+        <v>-0.7740000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1852</v>
+        <v>7.167800000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.957800000000001</v>
+        <v>-7.941800000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3839</v>
+        <v>6.7141</v>
       </c>
       <c r="E14" t="n">
-        <v>6.611</v>
+        <v>6.9487</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2271</v>
+        <v>-0.2346</v>
       </c>
       <c r="G14" t="n">
-        <v>5.49</v>
+        <v>5.4886</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9902</v>
+        <v>0.9932</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4997</v>
+        <v>4.4954</v>
       </c>
       <c r="J14" t="n">
-        <v>6.1444</v>
+        <v>6.1312</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0429</v>
+        <v>1.0375</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1015</v>
+        <v>5.0938</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6545</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0527</v>
+        <v>-0.0442</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6018</v>
+        <v>-0.5984</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4396</v>
+        <v>0.7703</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6247</v>
+        <v>-0.272</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0643</v>
+        <v>1.0423</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7609</v>
+        <v>3.1349</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8726</v>
+        <v>3.3884</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1118</v>
+        <v>-0.2535</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2011</v>
+        <v>0.2043</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2277</v>
+        <v>1.229</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0266</v>
+        <v>-1.0247</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8427</v>
+        <v>1.8382</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6936</v>
+        <v>1.6892</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1491</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6416</v>
+        <v>-1.6339</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4659</v>
+        <v>-0.4603</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1757</v>
+        <v>-1.1736</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8551</v>
+        <v>0.2265</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2336</v>
+        <v>-0.2418</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6214</v>
+        <v>0.4683</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0231</v>
+        <v>2.0212</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7963</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3418</v>
+        <v>1.4175</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7072</v>
+        <v>1.1099</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3654</v>
+        <v>0.3076</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7174</v>
+        <v>3.5904</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3938</v>
+        <v>3.4325</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6764</v>
+        <v>0.1579</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6914</v>
+        <v>4.678</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3932</v>
+        <v>3.6058</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2983</v>
+        <v>1.0722</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.974</v>
+        <v>-1.0876</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9994</v>
+        <v>-0.1733</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9746</v>
+        <v>-0.9143</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5903</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3741</v>
+        <v>0.3311</v>
       </c>
       <c r="T16" t="n">
-        <v>1.742</v>
+        <v>-0.1535</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6321</v>
+        <v>0.4846</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9281</v>
+        <v>1.2875</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5768</v>
+        <v>2.5051</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6488</v>
+        <v>-1.2177</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5486</v>
+        <v>1.717</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4726</v>
+        <v>2.3899</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0212</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0421</v>
+        <v>3.6796</v>
       </c>
       <c r="K17" t="n">
-        <v>0.985</v>
+        <v>3.3817</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0571</v>
+        <v>0.2979</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4935</v>
+        <v>-1.9626</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4577</v>
+        <v>-0.9918</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0358</v>
+        <v>-0.9708</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1359</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1359</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1754</v>
+        <v>1.3217</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6247</v>
+        <v>0.5571</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8</v>
+        <v>0.7645</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9318</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1594</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4808</v>
+        <v>1.1664</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6605</v>
+        <v>3.9217</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1797</v>
+        <v>-2.7553</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5952</v>
+        <v>0.5534</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4374</v>
+        <v>-0.4686</v>
       </c>
       <c r="I18" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.0359</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.0534</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-3.4825</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.4511</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.0314</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.1382</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.1382</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.272</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6785</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.9317</v>
+      </c>
+      <c r="W18" t="n">
         <v>0.1578</v>
       </c>
-      <c r="J18" t="n">
-        <v>4.693</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.6178</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.0752</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-1.0978</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.1804</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.9174</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-2.4991</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-3.4078</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.9087</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.6153999999999999</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-0.6247</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.009299999999999999</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2062</v>
+        <v>1.1544</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5312</v>
+        <v>1.2798</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7375</v>
+        <v>-0.1253</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6393</v>
+        <v>-0.7924</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7724</v>
+        <v>-2.4784</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1331</v>
+        <v>1.686</v>
       </c>
       <c r="J19" t="n">
-        <v>1.507</v>
+        <v>0.4832</v>
       </c>
       <c r="K19" t="n">
-        <v>1.78</v>
+        <v>-1.5868</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.273</v>
+        <v>2.0699</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8677</v>
+        <v>-1.2756</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0076</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8601</v>
+        <v>-0.384</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3631</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9301</v>
+        <v>0.3809</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2336</v>
+        <v>-0.2442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6964</v>
+        <v>0.6251</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.0212</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3102</v>
+        <v>-0.0885</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7125</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0227</v>
+        <v>0.6933</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7897</v>
+        <v>0.6407</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4787</v>
+        <v>1.7745</v>
       </c>
       <c r="I20" t="n">
-        <v>1.689</v>
+        <v>-1.1338</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4988</v>
+        <v>1.4994</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.577</v>
+        <v>1.7754</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0758</v>
+        <v>-0.276</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2885</v>
+        <v>-0.8587</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.0009</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3868</v>
+        <v>-0.8578</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4544</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6816</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0892</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8329</v>
+        <v>-0.0049</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2563</v>
+        <v>0.6415</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0231</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1825</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0313</v>
+        <v>-0.8869</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8804</v>
+        <v>1.9832</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9116</v>
+        <v>-2.8701</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.055</v>
+        <v>-0.0589</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3411</v>
+        <v>0.3391</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3961</v>
+        <v>-0.398</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2721</v>
+        <v>2.262</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.8996</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3674</v>
+        <v>1.3624</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3271</v>
+        <v>-2.3209</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5635</v>
+        <v>-0.5604</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7635</v>
+        <v>-1.7604</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2947</v>
+        <v>-0.1451</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.347</v>
+        <v>-0.2301</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0523</v>
+        <v>0.0849</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8778</v>
+        <v>-1.3568</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3113</v>
+        <v>1.5356</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1891</v>
+        <v>-2.8924</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3521</v>
+        <v>-1.3486</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8528</v>
+        <v>-0.8479</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4993</v>
+        <v>-0.5007</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9113</v>
+        <v>1.9051</v>
       </c>
       <c r="K22" t="n">
-        <v>0.432</v>
+        <v>0.4309</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4793</v>
+        <v>1.4741</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2634</v>
+        <v>-3.2536</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2848</v>
+        <v>-1.2788</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9786</v>
+        <v>-1.9749</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5256</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5553</v>
+        <v>-0.3207</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0296</v>
+        <v>0.3126</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.416</v>
+        <v>-4.4924</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2453</v>
+        <v>-0.0013</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6613</v>
+        <v>-4.4911</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3222</v>
+        <v>-3.3226</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7611</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5611</v>
+        <v>-2.559</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0117</v>
+        <v>0.0036</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6515</v>
+        <v>0.6443</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3339</v>
+        <v>-3.3262</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4126</v>
+        <v>-1.4078</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9213</v>
+        <v>-1.9184</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.18</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2336</v>
+        <v>-0.0049</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0537</v>
+        <v>0.1035</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.466399999999998</v>
+        <v>8.0502</v>
       </c>
       <c r="E24" t="n">
-        <v>22.0464</v>
+        <v>21.8893</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.58</v>
+        <v>-13.8391</v>
       </c>
       <c r="G24" t="n">
-        <v>6.672600000000001</v>
+        <v>6.671900000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5974</v>
+        <v>5.599699999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0751</v>
+        <v>1.0722</v>
       </c>
       <c r="J24" t="n">
-        <v>26.6145</v>
+        <v>26.5162</v>
       </c>
       <c r="K24" t="n">
-        <v>12.9237</v>
+        <v>12.8601</v>
       </c>
       <c r="L24" t="n">
-        <v>13.6909</v>
+        <v>13.6559</v>
       </c>
       <c r="M24" t="n">
-        <v>-19.942</v>
+        <v>-19.8442</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.3263</v>
+        <v>-7.260199999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-12.6156</v>
+        <v>-12.584</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.407899999999999</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.3593</v>
+        <v>-11.3817</v>
       </c>
       <c r="R24" t="n">
-        <v>7.951499999999999</v>
+        <v>7.9672</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4294</v>
+        <v>4.0189</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1665</v>
+        <v>-1.187</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5954</v>
+        <v>5.2058</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7725</v>
+        <v>0.7739999999999996</v>
       </c>
       <c r="W24" t="n">
-        <v>7.957700000000001</v>
+        <v>7.9419</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.185300000000001</v>
+        <v>-7.167999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104746_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104746_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.941800000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104746_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-7.167999999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
